--- a/output/graficos_dimensiones/comunal_d_env_a_2019_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:15</t>
+    <t xml:space="preserve">2026-09-10 01:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:28</t>
+    <t xml:space="preserve">2026-09-12 22:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:40</t>
+    <t xml:space="preserve">2026-09-24 00:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -499,7 +499,7 @@
         <v>2019</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>115.17</v>
+        <v>123.49</v>
       </c>
     </row>
     <row r="3">
@@ -516,7 +516,7 @@
         <v>2019</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>83.39</v>
+        <v>88.6</v>
       </c>
     </row>
     <row r="4">
@@ -533,7 +533,7 @@
         <v>2019</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>72.46</v>
+        <v>76.75</v>
       </c>
     </row>
     <row r="5">
@@ -550,7 +550,7 @@
         <v>2019</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>70.84</v>
+        <v>75.33</v>
       </c>
     </row>
     <row r="6">
@@ -567,7 +567,7 @@
         <v>2019</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>62.68</v>
+        <v>66.17</v>
       </c>
     </row>
     <row r="7">
@@ -584,7 +584,7 @@
         <v>2019</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>47.65</v>
+        <v>50.51</v>
       </c>
     </row>
     <row r="8">
@@ -601,7 +601,7 @@
         <v>2019</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>28.89</v>
+        <v>30.71</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:08</t>
+    <t xml:space="preserve">2026-10-02 16:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:06</t>
+    <t xml:space="preserve">2026-10-05 16:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
